--- a/트리거 관찰기.xlsx
+++ b/트리거 관찰기.xlsx
@@ -253,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -319,6 +319,54 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -662,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="4.42578125" customWidth="1" min="1" max="1"/>
@@ -676,15 +724,15 @@
     <col width="28.42578125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="59" customFormat="1" customHeight="1" s="21">
-      <c r="B1" s="19" t="inlineStr">
+    <row r="1" ht="15" customFormat="1" customHeight="1" s="21">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>아이덴티티 디자인 프로젝트 트리거 관찰하기 Sheet</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="163" customHeight="1" thickBot="1">
-      <c r="B2" s="20" t="inlineStr">
+    <row r="2" ht="105" customHeight="1" thickBot="1">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>1. 일주일간 여러분이 쓰신 트리거를 모두 프린트아웃하세요. 한 권의 책을 읽는다는 마음으로 쭉~ 읽어보세요.
 2. 트리거를 읽으면서 여러분이 강조했거나, 중요하다고 얘기하는 것들, 혹은 여러분의 행동이나 관계 등을 나타내는 단어 등등을 모두 색인해보세요. 
@@ -702,43 +750,43 @@
       <c r="G2" s="22" t="n"/>
       <c r="H2" s="22" t="n"/>
     </row>
-    <row r="3" ht="50" customFormat="1" customHeight="1" s="9">
-      <c r="B3" s="10" t="inlineStr">
+    <row r="3" ht="30" customFormat="1" customHeight="1" s="9">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>테마</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>트리거를 하면서 새롭게 깨닫거나, 
 알게된 것(#로 정리)</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>내가 인생에서 중요하게 
 생각하는 가치에 관한 단어</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>내가 사람과의 관계에서 중요하게 
 생각하는 것에 관한 단어</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>내가 어떤 행동을 할 때 
 중요하게 생각하는 것에 관한 단어</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>내가 관심 있는 
 사람이나, 산업, 대상에 관한 것</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>내가 잘 하거나 또는 좋아하는 활동에 
 관한 단어</t>
@@ -747,38 +795,38 @@
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="8" t="n"/>
     </row>
-    <row r="4" ht="122" customFormat="1" customHeight="1" s="9">
-      <c r="B4" s="11" t="inlineStr">
+    <row r="4" ht="30" customFormat="1" customHeight="1" s="9">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>트리거 넘버</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>- 나는 어렸을 때, 항상 배워야 한다고 생각을 했다. 배움만이 가치있는 거라고 생각했다…..
 - 그때 깨달았던 것 같다. 나는 늘 성장에 목말라 있다는 걸. 퇴사하고 싶었던 것도, 나는 앞으로 나아가고 싶었다….</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>- 회사에서 정말 좋아했던 선배가 있었는데, 그 선배랑은 어떤 얘기든 할 수 있었다. 그래서 그때 누군가의 이야기를 들어준다는 건 굉장한 일이라고 생각했다…. 
 - 저 사람은 왜 그럴까? 쟤는 왜 힘들다고 하지? 등등 이렇게 사람들을 관찰하는 것 자체가 나에게는 매우 흥미로웠다….</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>- 무조건 교환학생으로 가야겠다고 생각한 건, 이때가 아니면 더 넓은 세상을 못볼 거라고 생각했기 때문이었던 것 같다. 
 - 여행을 할 때면 나는 늘 시장을 가는 걸 좋아했다. 시장의 곳곳을 다니면서 그 지역 사람들이 사는 걸 관찰하는 게 좋았던 것 같다….</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t>- 인턴 때 신규산업을 위한 리서치를 했는데, 그때 우리나라의 공공 의료서비스에 대한 조사를 했다. 그때 얼마나 의료서비스의 혜택을 못받는 사람들이 정말 안타까웠다… 
 - 내가 자주 보는 브랜드들은 대부분, 이케아, 무인양품 등과 같은 라이프스타일에 관련된 서비스들이다…</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>- 어렸을 때 부터 뭔가 만드는 걸 좋아했다. 생각해보면 만드는 것보다 생각하는 걸 좋아했던 것 같다. 만들어내는 건 생각하는 걸 표현한 거였다. 
 - 일을 할 때도 기획하는 과정이 좋았다. 새로운 아이디어를 내고, 만들어내는 그 과정들이 나에게는 매우 흥미있었다….</t>
@@ -787,13 +835,13 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
     </row>
-    <row r="5" ht="53" customFormat="1" customHeight="1" s="8">
-      <c r="B5" s="13" t="inlineStr">
+    <row r="5" ht="75" customFormat="1" customHeight="1" s="8">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>no. 1</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>#행복은 순간적인 감정이 아니다
 #행복은 보고 느끼는 대상이다
@@ -801,7 +849,7 @@
 행복은 가진 것의 양보다, 내가 반복해서 주의를 기울이는 경험과 그것을 가능하게 하는 환경에서 만들어진다.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>- 경제적 독립이 자아실현의 첫 번째 조건이다
 - 즐거움과 목적의식이 균형을 이룰 때 더 깊은 행복을 느낀다
@@ -809,32 +857,32 @@
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>- 행복한 행동이 자연스럽게 일어나도록 환경을 설계해야 한다
 - 의지력만 믿을 것이 아니라, 반복이 가능하도록 환경을 만드는 것이 중요하다</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>- 여행 (새로운 것을 보고 경험하는 것)
 - 경제적 독립</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="34" t="inlineStr">
         <is>
           <t>- 여행 — 새로운 것을 보고 듣고 맛보고 경험하는 것
 - 새로운 환경에 적응하며 새로운 무언가를 받아들이는 것</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="66" customFormat="1" customHeight="1" s="8">
-      <c r="B6" s="13" t="inlineStr">
+    <row r="6" ht="75" customFormat="1" customHeight="1" s="8">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>no. 2</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>#성공의 재정의
 #복사본이 아닌 원본 성공
@@ -842,44 +890,44 @@
 성공은 남이 정해준 경쟁의 결과가 아니라, 내가 어떤 삶을 가치 있게 여기는지에 따라 다시 정의되어야 한다.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>- 나는 늘 남들이 정해놓은 방식보다 자기만의 방식으로 살아왔다
 - 성공이란 내 능력과 시간으로 주변 사람의 문제를 해결해주고 그들이 잘 살도록 돕는 것, 그 과정에서 내가 즐거울 때</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>- 외국인 친구들이 집을 구할 때, 비자 문제, 원하는 물건을 살 때 흥정까지 — 내가 직접 나서서 해결해줬다. 그때가 즐거웠다.
 - 회사에서 정말 좋아했던 선배랑은 어떤 얘기든 할 수 있었다</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>- 다양한 경험을 통해 스스로 길을 만드는 삶
 - 정해진 커리어보다 나만의 방식으로 성취를 만들어왔다</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>- 동남아 시장 화장품 판매 사업
 - 라이프스타일 브랜드 (이케아, 무인양품)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>- 아이디어를 시각화하고 사람들 앞에서 설득하는 것
 - 외국인 친구들 돕기, 커뮤니케이션</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="61" customFormat="1" customHeight="1" s="8">
-      <c r="B7" s="13" t="inlineStr">
+    <row r="7" ht="90" customFormat="1" customHeight="1" s="8">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>no. 3</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>#본질과 비본질
 #바쁨의 버블
@@ -888,34 +936,34 @@
 삶의 우선순위를 스스로 정하지 않으면 결국 남이 정해주게 된다.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>- 나를 위한 시간 — 좋아하는 사람들과 만나고, 여행을 가고, 자기개발을 하는 시간이 반드시 있어야 한다
 - 경제적 독립과 자립 — 내가 나답게 살 수 있는 환경을 만드는 첫 번째 조건
 - 내가 설계한 일을 하는 것 — 남이 정해준 커리어가 아니라</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>- 진정한 배려는 내 기준이 아니라 상대의 기준에서 출발해야 한다
 - 형식 없이 서로를 있는 그대로 대하는 관계가 나에게 더 맞는다
 - 관계에서 중요한 것은 소속감이나 의무가 아니라 진짜 통하는 것</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>- 본질적인 소수에만 집중하는 것
 - 불필요한 것을 걷어낼 때 비로소 본질이 드러난다
 - 내가 충전되고 평온할 때 비로소 주변에도 좋은 에너지를 줄 수 있다</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>- 외국인 친구들, 다양한 문화
 - 더 넓은 세상 (미국 어학연수에서 느낀 해방감과 자유)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>- 여행, 자기개발
 - 좋아하는 사람들과 만나는 것
@@ -923,13 +971,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customFormat="1" customHeight="1" s="8">
-      <c r="B8" s="13" t="inlineStr">
+    <row r="8" ht="90" customFormat="1" customHeight="1" s="8">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>no. 4</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>#나음vs다름
 #내가 좋아하는 것의 이유 찾기
@@ -938,27 +986,27 @@
 크리에이티브함은 더하는 것이 아니라 빼는 것에서 온다. 좋아함의 이유를 레이어 아래까지 내려가서 찾는 것.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>- 하찮은 것을 값진 것으로 만드는 발표력이 내게 있다는 것을 깨달았다
 - 큰 물에서 놀아야 더 큰 사람이 될 수 있다
 - 업무 스킬보다 전체 흐름을 보는 눈이 생겼다</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>- 내 시간과 노력과 지식을 동원하여 남에게 도움을 주면 기쁘다
 - 누군가 내게 도움을 받고 고마웠다고 말해주면 뿌듯하다</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>- 발표를 어떻게 할지를 먼저 생각했다 — 하찮은 것에 의미를 부여하는 방식
 - 실력이 부족해도 스토리텔러로서, 공간기획자로서 일을 할 수 있겠구나
 - 저렴하게 사거나 가치 있게 파는 것을 잘한다. 이윤을 창출하면 성취감을 느낀다</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>- 공간기획, 팝업스토어, 전시디자인
 - 동남아 화장품 판매
@@ -966,7 +1014,7 @@
 - 웰니스 센터 (장기 목표)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>- 발표하기, 스토리텔링
 - 리서치하기
@@ -975,39 +1023,39 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customFormat="1" customHeight="1" s="8" thickBot="1">
-      <c r="B9" s="14" t="inlineStr">
+    <row r="9" ht="45" customFormat="1" customHeight="1" s="8" thickBot="1">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>no. 5</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>자기 삶에 충실하면서도 마음의 여유가 넘치는 것이 이상적으로 느껴졌다
 지금 하는 일들이 목적지를 향해 가는 과정이라면 즐겁게 할 수 있을 것 같다</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>- 여유와 마음의 평온
 - 목적지가 있는 삶 — 지금 하는 것들을 과정으로 보는 것</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>- 부업 (동남아 화장품) — 홀로 서는 방법을 배우고, 자본 관리를 배우는 과정
 - 알바 — 요즘 일자리에 대한 견해를 높일 수 있는 경험
 - 좌담회 — 기업이 무엇을 준비하는지, 트렌드 흐름 파악</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>- AI, 창업, 사업 스킬
 - 트렌드 (어떤 제품, 어떤 음식)</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="38" t="inlineStr">
         <is>
           <t>- 동남아 화장품 부업
 - AI 강의 수강, 사업 스킬 배우기
@@ -1015,7 +1063,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
@@ -1024,7 +1072,7 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1">
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
@@ -1033,7 +1081,7 @@
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
@@ -1042,7 +1090,7 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
@@ -1051,7 +1099,7 @@
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
@@ -1060,7 +1108,7 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1">
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
@@ -1069,7 +1117,7 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1">
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
@@ -1078,7 +1126,7 @@
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1">
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
@@ -1087,7 +1135,7 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1">
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
@@ -1096,7 +1144,7 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1">
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
@@ -1105,7 +1153,7 @@
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1">
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
@@ -1114,7 +1162,7 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1">
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>

--- a/트리거 관찰기.xlsx
+++ b/트리거 관찰기.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -76,6 +76,15 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -253,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -366,6 +375,48 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,26 +764,27 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col width="4.42578125" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="24.85546875" customWidth="1" min="3" max="3"/>
-    <col width="30.5703125" customWidth="1" min="4" max="4"/>
-    <col width="33.85546875" customWidth="1" min="5" max="5"/>
-    <col width="32.140625" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="29.42578125" customWidth="1" min="8" max="8"/>
-    <col width="28.42578125" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customFormat="1" customHeight="1" s="21">
-      <c r="B1" s="23" t="inlineStr">
+    <row r="1" ht="85" customFormat="1" customHeight="1" s="21">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>아이덴티티 디자인 프로젝트 트리거 관찰하기 Sheet</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="105" customHeight="1" thickBot="1">
-      <c r="B2" s="24" t="inlineStr">
+    <row r="2" ht="1030" customHeight="1" thickBot="1">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>1. 일주일간 여러분이 쓰신 트리거를 모두 프린트아웃하세요. 한 권의 책을 읽는다는 마음으로 쭉~ 읽어보세요.
 2. 트리거를 읽으면서 여러분이 강조했거나, 중요하다고 얘기하는 것들, 혹은 여러분의 행동이나 관계 등을 나타내는 단어 등등을 모두 색인해보세요. 
@@ -750,43 +802,43 @@
       <c r="G2" s="22" t="n"/>
       <c r="H2" s="22" t="n"/>
     </row>
-    <row r="3" ht="30" customFormat="1" customHeight="1" s="9">
-      <c r="B3" s="25" t="inlineStr">
+    <row r="3" ht="44.5" customFormat="1" customHeight="1" s="9">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>테마</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>트리거를 하면서 새롭게 깨닫거나, 
 알게된 것(#로 정리)</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>내가 인생에서 중요하게 
 생각하는 가치에 관한 단어</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>내가 사람과의 관계에서 중요하게 
 생각하는 것에 관한 단어</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>내가 어떤 행동을 할 때 
 중요하게 생각하는 것에 관한 단어</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="42" t="inlineStr">
         <is>
           <t>내가 관심 있는 
 사람이나, 산업, 대상에 관한 것</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="43" t="inlineStr">
         <is>
           <t>내가 잘 하거나 또는 좋아하는 활동에 
 관한 단어</t>
@@ -795,38 +847,38 @@
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="8" t="n"/>
     </row>
-    <row r="4" ht="30" customFormat="1" customHeight="1" s="9">
-      <c r="B4" s="28" t="inlineStr">
+    <row r="4" ht="166" customFormat="1" customHeight="1" s="9">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>트리거 넘버</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>- 나는 어렸을 때, 항상 배워야 한다고 생각을 했다. 배움만이 가치있는 거라고 생각했다…..
 - 그때 깨달았던 것 같다. 나는 늘 성장에 목말라 있다는 걸. 퇴사하고 싶었던 것도, 나는 앞으로 나아가고 싶었다….</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>- 회사에서 정말 좋아했던 선배가 있었는데, 그 선배랑은 어떤 얘기든 할 수 있었다. 그래서 그때 누군가의 이야기를 들어준다는 건 굉장한 일이라고 생각했다…. 
 - 저 사람은 왜 그럴까? 쟤는 왜 힘들다고 하지? 등등 이렇게 사람들을 관찰하는 것 자체가 나에게는 매우 흥미로웠다….</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>- 무조건 교환학생으로 가야겠다고 생각한 건, 이때가 아니면 더 넓은 세상을 못볼 거라고 생각했기 때문이었던 것 같다. 
 - 여행을 할 때면 나는 늘 시장을 가는 걸 좋아했다. 시장의 곳곳을 다니면서 그 지역 사람들이 사는 걸 관찰하는 게 좋았던 것 같다….</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="45" t="inlineStr">
         <is>
           <t>- 인턴 때 신규산업을 위한 리서치를 했는데, 그때 우리나라의 공공 의료서비스에 대한 조사를 했다. 그때 얼마나 의료서비스의 혜택을 못받는 사람들이 정말 안타까웠다… 
 - 내가 자주 보는 브랜드들은 대부분, 이케아, 무인양품 등과 같은 라이프스타일에 관련된 서비스들이다…</t>
         </is>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>- 어렸을 때 부터 뭔가 만드는 걸 좋아했다. 생각해보면 만드는 것보다 생각하는 걸 좋아했던 것 같다. 만들어내는 건 생각하는 걸 표현한 거였다. 
 - 일을 할 때도 기획하는 과정이 좋았다. 새로운 아이디어를 내고, 만들어내는 그 과정들이 나에게는 매우 흥미있었다….</t>
@@ -835,13 +887,13 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
     </row>
-    <row r="5" ht="75" customFormat="1" customHeight="1" s="8">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5" ht="152.5" customFormat="1" customHeight="1" s="8">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>no. 1</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>#행복은 순간적인 감정이 아니다
 #행복은 보고 느끼는 대상이다
@@ -849,7 +901,7 @@
 행복은 가진 것의 양보다, 내가 반복해서 주의를 기울이는 경험과 그것을 가능하게 하는 환경에서 만들어진다.</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>- 경제적 독립이 자아실현의 첫 번째 조건이다
 - 즐거움과 목적의식이 균형을 이룰 때 더 깊은 행복을 느낀다
@@ -857,32 +909,32 @@
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>- 행복한 행동이 자연스럽게 일어나도록 환경을 설계해야 한다
 - 의지력만 믿을 것이 아니라, 반복이 가능하도록 환경을 만드는 것이 중요하다</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="48" t="inlineStr">
         <is>
           <t>- 여행 (새로운 것을 보고 경험하는 것)
 - 경제적 독립</t>
         </is>
       </c>
-      <c r="H5" s="34" t="inlineStr">
+      <c r="H5" s="49" t="inlineStr">
         <is>
           <t>- 여행 — 새로운 것을 보고 듣고 맛보고 경험하는 것
 - 새로운 환경에 적응하며 새로운 무언가를 받아들이는 것</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="75" customFormat="1" customHeight="1" s="8">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6" ht="112" customFormat="1" customHeight="1" s="8">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>no. 2</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>#성공의 재정의
 #복사본이 아닌 원본 성공
@@ -890,44 +942,44 @@
 성공은 남이 정해준 경쟁의 결과가 아니라, 내가 어떤 삶을 가치 있게 여기는지에 따라 다시 정의되어야 한다.</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>- 나는 늘 남들이 정해놓은 방식보다 자기만의 방식으로 살아왔다
 - 성공이란 내 능력과 시간으로 주변 사람의 문제를 해결해주고 그들이 잘 살도록 돕는 것, 그 과정에서 내가 즐거울 때</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>- 외국인 친구들이 집을 구할 때, 비자 문제, 원하는 물건을 살 때 흥정까지 — 내가 직접 나서서 해결해줬다. 그때가 즐거웠다.
 - 회사에서 정말 좋아했던 선배랑은 어떤 얘기든 할 수 있었다</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>- 다양한 경험을 통해 스스로 길을 만드는 삶
 - 정해진 커리어보다 나만의 방식으로 성취를 만들어왔다</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="48" t="inlineStr">
         <is>
           <t>- 동남아 시장 화장품 판매 사업
 - 라이프스타일 브랜드 (이케아, 무인양품)</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="49" t="inlineStr">
         <is>
           <t>- 아이디어를 시각화하고 사람들 앞에서 설득하는 것
 - 외국인 친구들 돕기, 커뮤니케이션</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customFormat="1" customHeight="1" s="8">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7" ht="139" customFormat="1" customHeight="1" s="8">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>no. 3</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>#본질과 비본질
 #바쁨의 버블
@@ -936,34 +988,34 @@
 삶의 우선순위를 스스로 정하지 않으면 결국 남이 정해주게 된다.</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>- 나를 위한 시간 — 좋아하는 사람들과 만나고, 여행을 가고, 자기개발을 하는 시간이 반드시 있어야 한다
 - 경제적 독립과 자립 — 내가 나답게 살 수 있는 환경을 만드는 첫 번째 조건
 - 내가 설계한 일을 하는 것 — 남이 정해준 커리어가 아니라</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>- 진정한 배려는 내 기준이 아니라 상대의 기준에서 출발해야 한다
 - 형식 없이 서로를 있는 그대로 대하는 관계가 나에게 더 맞는다
 - 관계에서 중요한 것은 소속감이나 의무가 아니라 진짜 통하는 것</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>- 본질적인 소수에만 집중하는 것
 - 불필요한 것을 걷어낼 때 비로소 본질이 드러난다
 - 내가 충전되고 평온할 때 비로소 주변에도 좋은 에너지를 줄 수 있다</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="48" t="inlineStr">
         <is>
           <t>- 외국인 친구들, 다양한 문화
 - 더 넓은 세상 (미국 어학연수에서 느낀 해방감과 자유)</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="49" t="inlineStr">
         <is>
           <t>- 여행, 자기개발
 - 좋아하는 사람들과 만나는 것
@@ -971,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customFormat="1" customHeight="1" s="8">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8" ht="139" customFormat="1" customHeight="1" s="8">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>no. 4</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>#나음vs다름
 #내가 좋아하는 것의 이유 찾기
@@ -986,27 +1038,27 @@
 크리에이티브함은 더하는 것이 아니라 빼는 것에서 온다. 좋아함의 이유를 레이어 아래까지 내려가서 찾는 것.</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>- 하찮은 것을 값진 것으로 만드는 발표력이 내게 있다는 것을 깨달았다
 - 큰 물에서 놀아야 더 큰 사람이 될 수 있다
 - 업무 스킬보다 전체 흐름을 보는 눈이 생겼다</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>- 내 시간과 노력과 지식을 동원하여 남에게 도움을 주면 기쁘다
 - 누군가 내게 도움을 받고 고마웠다고 말해주면 뿌듯하다</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="48" t="inlineStr">
         <is>
           <t>- 발표를 어떻게 할지를 먼저 생각했다 — 하찮은 것에 의미를 부여하는 방식
 - 실력이 부족해도 스토리텔러로서, 공간기획자로서 일을 할 수 있겠구나
 - 저렴하게 사거나 가치 있게 파는 것을 잘한다. 이윤을 창출하면 성취감을 느낀다</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" s="48" t="inlineStr">
         <is>
           <t>- 공간기획, 팝업스토어, 전시디자인
 - 동남아 화장품 판매
@@ -1014,7 +1066,7 @@
 - 웰니스 센터 (장기 목표)</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="49" t="inlineStr">
         <is>
           <t>- 발표하기, 스토리텔링
 - 리서치하기
@@ -1023,39 +1075,39 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customFormat="1" customHeight="1" s="8" thickBot="1">
-      <c r="B9" s="36" t="inlineStr">
+    <row r="9" ht="125.5" customFormat="1" customHeight="1" s="8" thickBot="1">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>no. 5</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>자기 삶에 충실하면서도 마음의 여유가 넘치는 것이 이상적으로 느껴졌다
 지금 하는 일들이 목적지를 향해 가는 과정이라면 즐겁게 할 수 있을 것 같다</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>- 여유와 마음의 평온
 - 목적지가 있는 삶 — 지금 하는 것들을 과정으로 보는 것</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="51" t="inlineStr">
         <is>
           <t>- 부업 (동남아 화장품) — 홀로 서는 방법을 배우고, 자본 관리를 배우는 과정
 - 알바 — 요즘 일자리에 대한 견해를 높일 수 있는 경험
 - 좌담회 — 기업이 무엇을 준비하는지, 트렌드 흐름 파악</t>
         </is>
       </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="G9" s="51" t="inlineStr">
         <is>
           <t>- AI, 창업, 사업 스킬
 - 트렌드 (어떤 제품, 어떤 음식)</t>
         </is>
       </c>
-      <c r="H9" s="38" t="inlineStr">
+      <c r="H9" s="52" t="inlineStr">
         <is>
           <t>- 동남아 화장품 부업
 - AI 강의 수강, 사업 스킬 배우기
@@ -1063,7 +1115,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="17.5" customHeight="1">
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
@@ -1072,7 +1124,7 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="17.5" customHeight="1">
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="n"/>
       <c r="F11" s="8" t="n"/>
@@ -1081,7 +1133,7 @@
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="17.5" customHeight="1">
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
@@ -1090,7 +1142,7 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="17.5" customHeight="1">
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
@@ -1099,7 +1151,7 @@
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="17.5" customHeight="1">
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
@@ -1108,7 +1160,7 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="17.5" customHeight="1">
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
@@ -1117,7 +1169,7 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="17.5" customHeight="1">
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n"/>
@@ -1126,7 +1178,7 @@
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="17.5" customHeight="1">
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
@@ -1135,7 +1187,7 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="17.5" customHeight="1">
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
@@ -1144,7 +1196,7 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="17.5" customHeight="1">
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
@@ -1153,7 +1205,7 @@
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="17.5" customHeight="1">
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
@@ -1162,7 +1214,7 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="17.5" customHeight="1">
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
